--- a/ARM Functions/Item Edits/Blastoisinite.xlsx
+++ b/ARM Functions/Item Edits/Blastoisinite.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Item Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B12C73-1B7B-4C41-A6DF-8EA6093DCB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2723754-54EB-436A-B7C7-2CE92A72C57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{6B563214-6527-4E5F-B5EA-E821D6DED3A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Code" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="82">
   <si>
     <t>7080BDE8</t>
   </si>
@@ -273,21 +273,12 @@
     <t>EF16FEEB</t>
   </si>
   <si>
-    <t>0E00001A</t>
-  </si>
-  <si>
-    <t>BA40FEEB</t>
-  </si>
-  <si>
     <t>0800001A</t>
   </si>
   <si>
     <t>1200A0E3</t>
   </si>
   <si>
-    <t>E516FEEB</t>
-  </si>
-  <si>
     <t>010C40E2</t>
   </si>
   <si>
@@ -306,10 +297,13 @@
     <t>3040BDE8</t>
   </si>
   <si>
-    <t>5903FEEA</t>
-  </si>
-  <si>
     <t>3080BDE8</t>
+  </si>
+  <si>
+    <t>EB16FEEB</t>
+  </si>
+  <si>
+    <t>5F03FEEA</t>
   </si>
 </sst>
 </file>
@@ -728,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B45B0BF-76E7-4635-9005-9D6B1877FAE8}">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -1096,7 +1090,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="str">
-        <f t="shared" ref="A30:A52" si="2">DEC2HEX(HEX2DEC(A30)+4,8)</f>
+        <f t="shared" ref="A31:A46" si="2">DEC2HEX(HEX2DEC(A30)+4,8)</f>
         <v>00101F88</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -1168,226 +1162,143 @@
         <v>71</v>
       </c>
       <c r="C36" s="4" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A52)</f>
-        <v>bne 0x00101FDC</v>
+        <f>_xlfn.CONCAT("bne 0x",A46)</f>
+        <v>bne 0x00101FC4</v>
       </c>
       <c r="D36" s="4"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="8" t="str">
+      <c r="A37" s="10" t="str">
         <f t="shared" si="2"/>
         <v>00101FA0</v>
       </c>
-      <c r="B37" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>29</v>
+      <c r="B37" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="8" t="str">
+      <c r="A38" s="10" t="str">
         <f t="shared" si="2"/>
         <v>00101FA4</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="8"/>
+      <c r="B38" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="10"/>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="8" t="str">
+      <c r="A39" s="10" t="str">
         <f t="shared" si="2"/>
         <v>00101FA8</v>
       </c>
-      <c r="B39" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" s="8"/>
+      <c r="B39" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="6" t="str">
+      <c r="A40" s="10" t="str">
         <f t="shared" si="2"/>
         <v>00101FAC</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>33</v>
-      </c>
+      <c r="B40" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D40" s="10"/>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="6" t="str">
+      <c r="A41" s="10" t="str">
         <f t="shared" si="2"/>
         <v>00101FB0</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D41" s="6"/>
+      <c r="B41" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="10" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A46)</f>
+        <v>bne 0x00101FC4</v>
+      </c>
+      <c r="D41" s="10"/>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="6" t="str">
+      <c r="A42" s="2" t="str">
         <f t="shared" si="2"/>
         <v>00101FB4</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" s="6" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A52)</f>
-        <v>bne 0x00101FDC</v>
-      </c>
-      <c r="D42" s="6"/>
+      <c r="B42" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="10" t="str">
+      <c r="A43" s="2" t="str">
         <f t="shared" si="2"/>
         <v>00101FB8</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>52</v>
+      <c r="B43" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="10" t="str">
+      <c r="A44" s="2" t="str">
         <f t="shared" si="2"/>
         <v>00101FBC</v>
       </c>
-      <c r="B44" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D44" s="10"/>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>00101FC0</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>00101FC4</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D46" s="10"/>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>00101FC8</v>
-      </c>
-      <c r="B47" s="10" t="s">
+      <c r="B44" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C47" s="10" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A52)</f>
-        <v>bne 0x00101FDC</v>
-      </c>
-      <c r="D47" s="10"/>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>00101FCC</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>00101FD0</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>00101FD4</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" s="2" t="str">
+      <c r="C44" s="2" t="str">
         <f>SUBSTITUTE(C30,"push","pop")</f>
         <v>pop {r4, r5, lr}</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>00101FD8</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C51" s="2" t="s">
+    <row r="45" spans="1:4">
+      <c r="A45" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>00101FC0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>00101FDC</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" s="2" t="str">
-        <f>SUBSTITUTE(C50,"lr","pc")</f>
+    <row r="46" spans="1:4">
+      <c r="A46" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>00101FC4</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="2" t="str">
+        <f>SUBSTITUTE(C44,"lr","pc")</f>
         <v>pop {r4, r5, pc}</v>
       </c>
     </row>
